--- a/Tools.Config/GameConfig/Datas/building.xlsx
+++ b/Tools.Config/GameConfig/Datas/building.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1540,6 +1540,63 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>401</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>局内商店</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Building_BattleShop</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>地图商店建筑</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>巨魔选中后可打开局内商店</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
